--- a/archs/pssai_solo_coder/risultati/report_global.xlsx
+++ b/archs/pssai_solo_coder/risultati/report_global.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\MAGISTRALE RIZIERO\Tesi who Tesi what\git\PSSAI_Core\archs\pssai_solo_coder\risultati\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B600431-982E-4541-AA84-D51D0C2DD6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E00F5F33-3E0D-48C2-A7C0-8532861E31D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21795" yWindow="1410" windowWidth="28800" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Code_Similarity_Metrics" sheetId="1" r:id="rId1"/>
@@ -8186,19 +8186,19 @@
         <v>8</v>
       </c>
       <c r="E3">
-        <v>0.80851063829787229</v>
+        <v>0.70851063829787198</v>
       </c>
       <c r="F3">
-        <v>0.88120567375886538</v>
+        <v>0.831205673758865</v>
       </c>
       <c r="G3">
         <v>0.24717355005112709</v>
       </c>
       <c r="H3">
-        <v>0.91276595744680844</v>
+        <v>0.88276595744680797</v>
       </c>
       <c r="I3">
-        <v>0.34042553191489361</v>
+        <v>0.400425531914894</v>
       </c>
       <c r="J3">
         <v>0.75163922266619965</v>
